--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -1718,7 +1718,7 @@
         <v>131196450</v>
       </c>
       <c r="B10" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131196448</v>
       </c>
       <c r="B11" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131196451</v>
+        <v>131196449</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>57064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,37 +1973,50 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500318</v>
+        <v>500203</v>
       </c>
       <c r="R12" t="n">
-        <v>7016201</v>
+        <v>7016330</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2038,13 +2051,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st födosökande järpar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2068,10 +2085,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131196449</v>
+        <v>131196451</v>
       </c>
       <c r="B13" t="n">
-        <v>57064</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,50 +2096,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500203</v>
+        <v>500318</v>
       </c>
       <c r="R13" t="n">
-        <v>7016330</v>
+        <v>7016201</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2157,17 +2161,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st födosökande järpar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>131196452</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131196439</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>131196442</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>131196445</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>131196443</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>131196446</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131196440</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>131196444</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>131196441</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>131196450</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131196448</v>
       </c>
       <c r="B11" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131196449</v>
+        <v>131196451</v>
       </c>
       <c r="B12" t="n">
-        <v>57064</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,50 +1973,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500203</v>
+        <v>500318</v>
       </c>
       <c r="R12" t="n">
-        <v>7016330</v>
+        <v>7016201</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2051,17 +2038,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st födosökande järpar.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2085,10 +2068,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131196451</v>
+        <v>131196449</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>57066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,37 +2079,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500318</v>
+        <v>500203</v>
       </c>
       <c r="R13" t="n">
-        <v>7016201</v>
+        <v>7016330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2161,13 +2157,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st födosökande järpar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>131196452</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>131196447</v>
       </c>
       <c r="B15" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131196439</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>131196442</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>131196445</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>131196443</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>131196446</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131196440</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>131196444</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>131196441</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>131196450</v>
       </c>
       <c r="B10" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131196448</v>
       </c>
       <c r="B11" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>131196451</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>131196449</v>
       </c>
       <c r="B13" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>131196452</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>131196447</v>
       </c>
       <c r="B15" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131196452</v>
+        <v>131196447</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>58046</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,37 +2202,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500345</v>
+        <v>500269</v>
       </c>
       <c r="R14" t="n">
-        <v>7016371</v>
+        <v>7016195</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2267,13 +2280,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 st talltita.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2297,10 +2314,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131196447</v>
+        <v>131196452</v>
       </c>
       <c r="B15" t="n">
-        <v>58046</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2308,50 +2325,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500269</v>
+        <v>500345</v>
       </c>
       <c r="R15" t="n">
-        <v>7016195</v>
+        <v>7016371</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2386,17 +2390,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 st talltita.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131196439</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>131196442</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>131196445</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>131196443</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>131196446</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131196440</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>131196444</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>131196441</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>131196450</v>
       </c>
       <c r="B10" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131196448</v>
       </c>
       <c r="B11" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>131196451</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131196447</v>
+        <v>131196452</v>
       </c>
       <c r="B14" t="n">
-        <v>58046</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,50 +2202,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500269</v>
+        <v>500345</v>
       </c>
       <c r="R14" t="n">
-        <v>7016195</v>
+        <v>7016371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2280,17 +2267,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 st talltita.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2314,10 +2297,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131196452</v>
+        <v>131196447</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>58047</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2325,37 +2308,50 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500345</v>
+        <v>500269</v>
       </c>
       <c r="R15" t="n">
-        <v>7016371</v>
+        <v>7016195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2390,13 +2386,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 st talltita.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131196451</v>
+        <v>131196449</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>57067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,37 +1973,50 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500318</v>
+        <v>500203</v>
       </c>
       <c r="R12" t="n">
-        <v>7016201</v>
+        <v>7016330</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2038,13 +2051,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st födosökande järpar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2068,10 +2085,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131196449</v>
+        <v>131196451</v>
       </c>
       <c r="B13" t="n">
-        <v>57067</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,50 +2096,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500203</v>
+        <v>500318</v>
       </c>
       <c r="R13" t="n">
-        <v>7016330</v>
+        <v>7016201</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2157,17 +2161,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st födosökande järpar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131196452</v>
+        <v>131196447</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>58047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,37 +2202,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500345</v>
+        <v>500269</v>
       </c>
       <c r="R14" t="n">
-        <v>7016371</v>
+        <v>7016195</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2267,13 +2280,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 st talltita.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2297,10 +2314,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131196447</v>
+        <v>131196452</v>
       </c>
       <c r="B15" t="n">
-        <v>58047</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2308,50 +2325,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500269</v>
+        <v>500345</v>
       </c>
       <c r="R15" t="n">
-        <v>7016195</v>
+        <v>7016371</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2386,17 +2390,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 st talltita.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131196439</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>131196442</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>131196445</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>131196443</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>131196446</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131196440</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>131196444</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>131196441</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>131196450</v>
       </c>
       <c r="B10" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131196448</v>
       </c>
       <c r="B11" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131196449</v>
+        <v>131196451</v>
       </c>
       <c r="B12" t="n">
-        <v>57067</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,50 +1973,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500203</v>
+        <v>500318</v>
       </c>
       <c r="R12" t="n">
-        <v>7016330</v>
+        <v>7016201</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2051,17 +2038,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st födosökande järpar.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2085,10 +2068,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131196451</v>
+        <v>131196449</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>57070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,37 +2079,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500318</v>
+        <v>500203</v>
       </c>
       <c r="R13" t="n">
-        <v>7016201</v>
+        <v>7016330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2161,13 +2157,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st födosökande järpar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131196447</v>
+        <v>131196452</v>
       </c>
       <c r="B14" t="n">
-        <v>58047</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,50 +2202,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500269</v>
+        <v>500345</v>
       </c>
       <c r="R14" t="n">
-        <v>7016195</v>
+        <v>7016371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2280,17 +2267,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 st talltita.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2314,10 +2297,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131196452</v>
+        <v>131196447</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>58050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2325,37 +2308,50 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500345</v>
+        <v>500269</v>
       </c>
       <c r="R15" t="n">
-        <v>7016371</v>
+        <v>7016195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2390,13 +2386,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 st talltita.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131196439</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>131196442</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>131196445</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>131196443</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>131196446</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131196440</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>131196444</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>131196441</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>131196450</v>
       </c>
       <c r="B10" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131196448</v>
       </c>
       <c r="B11" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131196451</v>
+        <v>131196449</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>57071</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,37 +1973,50 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500318</v>
+        <v>500203</v>
       </c>
       <c r="R12" t="n">
-        <v>7016201</v>
+        <v>7016330</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2038,13 +2051,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st födosökande järpar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2068,10 +2085,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131196449</v>
+        <v>131196451</v>
       </c>
       <c r="B13" t="n">
-        <v>57070</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,50 +2096,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500203</v>
+        <v>500318</v>
       </c>
       <c r="R13" t="n">
-        <v>7016330</v>
+        <v>7016201</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2157,17 +2161,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st födosökande järpar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131196452</v>
+        <v>131196447</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>58051</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,37 +2202,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500345</v>
+        <v>500269</v>
       </c>
       <c r="R14" t="n">
-        <v>7016371</v>
+        <v>7016195</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2267,13 +2280,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 st talltita.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2297,10 +2314,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131196447</v>
+        <v>131196452</v>
       </c>
       <c r="B15" t="n">
-        <v>58050</v>
+        <v>79254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2308,50 +2325,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500269</v>
+        <v>500345</v>
       </c>
       <c r="R15" t="n">
-        <v>7016195</v>
+        <v>7016371</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2386,17 +2390,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 st talltita.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131196449</v>
+        <v>131196451</v>
       </c>
       <c r="B12" t="n">
-        <v>57071</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,50 +1973,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500203</v>
+        <v>500318</v>
       </c>
       <c r="R12" t="n">
-        <v>7016330</v>
+        <v>7016201</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2051,17 +2038,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st födosökande järpar.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2085,10 +2068,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131196451</v>
+        <v>131196449</v>
       </c>
       <c r="B13" t="n">
-        <v>79254</v>
+        <v>57071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,37 +2079,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500318</v>
+        <v>500203</v>
       </c>
       <c r="R13" t="n">
-        <v>7016201</v>
+        <v>7016330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2161,13 +2157,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st födosökande järpar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131196447</v>
+        <v>131196452</v>
       </c>
       <c r="B14" t="n">
-        <v>58051</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,50 +2202,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500269</v>
+        <v>500345</v>
       </c>
       <c r="R14" t="n">
-        <v>7016195</v>
+        <v>7016371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2280,17 +2267,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 st talltita.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2314,10 +2297,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131196452</v>
+        <v>131196447</v>
       </c>
       <c r="B15" t="n">
-        <v>79254</v>
+        <v>58051</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2325,37 +2308,50 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500345</v>
+        <v>500269</v>
       </c>
       <c r="R15" t="n">
-        <v>7016371</v>
+        <v>7016195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2390,13 +2386,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 st talltita.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131196439</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>131196442</v>
       </c>
       <c r="B3" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>131196445</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>131196443</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>131196446</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131196440</v>
       </c>
       <c r="B7" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>131196444</v>
       </c>
       <c r="B8" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>131196441</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>131196450</v>
       </c>
       <c r="B10" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>131196448</v>
       </c>
       <c r="B11" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>131196451</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>131196449</v>
       </c>
       <c r="B13" t="n">
-        <v>57071</v>
+        <v>57077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131196452</v>
+        <v>131196447</v>
       </c>
       <c r="B14" t="n">
-        <v>79254</v>
+        <v>58057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,37 +2202,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500345</v>
+        <v>500269</v>
       </c>
       <c r="R14" t="n">
-        <v>7016371</v>
+        <v>7016195</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2267,13 +2280,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 st talltita.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2297,10 +2314,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131196447</v>
+        <v>131196452</v>
       </c>
       <c r="B15" t="n">
-        <v>58051</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2308,50 +2325,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500269</v>
+        <v>500345</v>
       </c>
       <c r="R15" t="n">
-        <v>7016195</v>
+        <v>7016371</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2386,17 +2390,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 st talltita.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131196447</v>
+        <v>131196452</v>
       </c>
       <c r="B14" t="n">
-        <v>58057</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,50 +2202,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500269</v>
+        <v>500345</v>
       </c>
       <c r="R14" t="n">
-        <v>7016195</v>
+        <v>7016371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2280,17 +2267,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 st talltita.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2314,10 +2297,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131196452</v>
+        <v>131196447</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>58057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2325,37 +2308,50 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500345</v>
+        <v>500269</v>
       </c>
       <c r="R15" t="n">
-        <v>7016371</v>
+        <v>7016195</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2390,13 +2386,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 st talltita.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -1962,10 +1962,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131196451</v>
+        <v>131196449</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>57077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,37 +1973,50 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500318</v>
+        <v>500203</v>
       </c>
       <c r="R12" t="n">
-        <v>7016201</v>
+        <v>7016330</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2038,13 +2051,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st födosökande järpar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2068,10 +2085,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131196449</v>
+        <v>131196451</v>
       </c>
       <c r="B13" t="n">
-        <v>57077</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,50 +2096,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500203</v>
+        <v>500318</v>
       </c>
       <c r="R13" t="n">
-        <v>7016330</v>
+        <v>7016201</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2157,17 +2161,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st födosökande järpar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2191,10 +2191,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131196452</v>
+        <v>131196447</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>58057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,37 +2202,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500345</v>
+        <v>500269</v>
       </c>
       <c r="R14" t="n">
-        <v>7016371</v>
+        <v>7016195</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2267,13 +2280,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 st talltita.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2297,10 +2314,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131196447</v>
+        <v>131196452</v>
       </c>
       <c r="B15" t="n">
-        <v>58057</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2308,50 +2325,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500269</v>
+        <v>500345</v>
       </c>
       <c r="R15" t="n">
-        <v>7016195</v>
+        <v>7016371</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2386,17 +2390,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 st talltita.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131196439</v>
+        <v>131196448</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500162</v>
+        <v>500380</v>
       </c>
       <c r="R2" t="n">
-        <v>7016282</v>
+        <v>7016173</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,17 +751,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,17 +768,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131196442</v>
+        <v>131196446</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,7 +834,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -848,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500145</v>
+        <v>500268</v>
       </c>
       <c r="R3" t="n">
-        <v>7016300</v>
+        <v>7016174</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,17 +903,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,42 +931,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131196445</v>
+        <v>131196451</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -978,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500145</v>
+        <v>500318</v>
       </c>
       <c r="R4" t="n">
-        <v>7016290</v>
+        <v>7016201</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,38 +1007,19 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1065,42 +1037,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131196443</v>
+        <v>131196452</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1108,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500146</v>
+        <v>500345</v>
       </c>
       <c r="R5" t="n">
-        <v>7016293</v>
+        <v>7016371</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,38 +1113,19 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131196446</v>
+        <v>131196439</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500268</v>
+        <v>500162</v>
       </c>
       <c r="R6" t="n">
-        <v>7016174</v>
+        <v>7016282</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1226,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,17 +1245,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1328,7 +1276,7 @@
         <v>131196440</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1455,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131196444</v>
+        <v>131196441</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,10 +1446,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500145</v>
+        <v>500148</v>
       </c>
       <c r="R8" t="n">
-        <v>7016295</v>
+        <v>7016287</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1585,10 +1533,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131196441</v>
+        <v>131196442</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1628,10 +1576,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500148</v>
+        <v>500145</v>
       </c>
       <c r="R9" t="n">
-        <v>7016287</v>
+        <v>7016300</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1715,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131196450</v>
+        <v>131196443</v>
       </c>
       <c r="B10" t="n">
-        <v>91848</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,24 +1674,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1753,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500294</v>
+        <v>500146</v>
       </c>
       <c r="R10" t="n">
-        <v>7016193</v>
+        <v>7016293</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1791,13 +1744,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1836,10 +1793,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131196448</v>
+        <v>131196444</v>
       </c>
       <c r="B11" t="n">
-        <v>80365</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,26 +1804,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1874,10 +1836,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500380</v>
+        <v>500145</v>
       </c>
       <c r="R11" t="n">
-        <v>7016173</v>
+        <v>7016295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1912,13 +1874,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1929,22 +1895,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1962,10 +1923,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131196449</v>
+        <v>131196445</v>
       </c>
       <c r="B12" t="n">
-        <v>57077</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,16 +1934,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1990,33 +1951,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500203</v>
+        <v>500145</v>
       </c>
       <c r="R12" t="n">
-        <v>7016330</v>
+        <v>7016290</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2053,7 +2006,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Synobservation av 2 st födosökande järpar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2068,6 +2021,21 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2085,48 +2053,61 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131196451</v>
+        <v>131196449</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>57132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fäviken Sydväst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500318</v>
+        <v>500203</v>
       </c>
       <c r="R13" t="n">
-        <v>7016201</v>
+        <v>7016330</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2161,13 +2142,17 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st födosökande järpar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2194,7 +2179,7 @@
         <v>131196447</v>
       </c>
       <c r="B14" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2311,112 +2296,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>131196452</v>
-      </c>
-      <c r="B15" t="n">
-        <v>79260</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Fäviken Sydväst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>500345</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7016371</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1026-2026 artfynd.xlsx
+++ b/artfynd/A 1026-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196439</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196440</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,6 +1077,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196441</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1192,6 +1212,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196442</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1322,6 +1347,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196443</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1452,6 +1482,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196444</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1582,6 +1617,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196445</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1688,6 +1728,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196451</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1794,6 +1839,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196452</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1920,6 +1970,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196448</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2050,6 +2105,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196446</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2173,6 +2233,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196449</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2296,8 +2361,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131196447</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>